--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -809,6 +809,1079 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126028545</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rifallet uppe i skogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>483381</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6664345</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3 st ljudupptagningar av tjäderläten / sångljud.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126026452</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57809</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rifallet upp från mossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>483559</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6664311</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2 st ljudupptagningar av Talltita (Poecile montanus).</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126027986</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56834</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rifallet upp från mossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>483559</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6664311</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>03:14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>03:14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>3 st ljudupptagningar av Järpe (Tetrastes bonasia). En av ljudfilerna uppladdade på Xeno-canto.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126028950</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57811</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rifallet uppe i skogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>483381</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6664345</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>5 st ljudupptagningar av Talltita (poecile montanus).</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Blandskog i branter</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Silverfura</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126025893</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57811</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rifallet mot myr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>483598</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6664322</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>12 st ljudupptagningar av Talltita (Poecile montanus) kl. 07.41 - kl. 09.15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126026768</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rifallet upp från mossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>483559</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6664311</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>03:01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>03:01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Tre ljudupptagningar av tjäder mellan kl. 03.01 - kl. 04.54 den 15 juni 2025.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126027361</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57664</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rifallet upp från mossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>483559</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6664311</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>49 st ljudupptagningar av mindre hackspett (Dryobates minor)</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126029030</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57473</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rifallet uppe i skogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>483381</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6664345</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ljudupptagning av tornseglare på nära håll i gles sluttande barrskog.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126030775</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57933</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lövskogsdel, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>483431</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6664289</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>03:14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>03:14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Blandskog i branter</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Barrblandskog med stort lövinslag i brant terräng som gränsar mot sumpskog / myrmark</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,6 +921,16 @@
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -1039,6 +1049,16 @@
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -1153,6 +1173,16 @@
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -1292,6 +1322,16 @@
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1415,6 +1455,16 @@
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1533,6 +1583,16 @@
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1643,6 +1703,16 @@
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1757,6 +1827,16 @@
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1880,7 +1960,307 @@
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126043240</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56519</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fladdermusstation, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>483330</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6664403</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>23:22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>23:22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>12 st ljudupptagningar av Nordfladdermus (Eptesicus nilssonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering utförd av Emily Macgregor vid Naturcentrum.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126043322</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56526</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fladdermusstation, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>483330</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6664403</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>23:01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>23:01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>8 st ljudupptagningar av Vattenfladdermus (Myotis daubentonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering av ljudfiler utförd av Emily Macgregor vid Naturcentrum.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Gammal grov död rönn trolig boplats / viloplats</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia # Gammal grov död rönn trolig boplats / viloplats</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1841,10 +1841,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126030775</v>
+        <v>126043240</v>
       </c>
       <c r="B11" t="n">
-        <v>57933</v>
+        <v>56519</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,28 +1852,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103012</v>
+        <v>205998</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1881,24 +1882,20 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lövskogsdel, Dlr</t>
+          <t>Fladdermusstation, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483431</v>
+        <v>483330</v>
       </c>
       <c r="R11" t="n">
-        <v>6664289</v>
+        <v>6664403</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1922,22 +1919,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>03:14</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>03:14</t>
+          <t>23:22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>12 st ljudupptagningar av Nordfladdermus (Eptesicus nilssonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering utförd av Emily Macgregor vid Naturcentrum.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1951,12 +1953,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrblandskog med stort lövinslag i brant terräng som gränsar mot sumpskog / myrmark</t>
+          <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1974,37 +1976,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126043240</v>
+        <v>126043322</v>
       </c>
       <c r="B12" t="n">
-        <v>56519</v>
+        <v>56526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -2057,7 +2059,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2067,12 +2069,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>12 st ljudupptagningar av Nordfladdermus (Eptesicus nilssonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering utförd av Emily Macgregor vid Naturcentrum.</t>
+          <t>8 st ljudupptagningar av Vattenfladdermus (Myotis daubentonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering av ljudfiler utförd av Emily Macgregor vid Naturcentrum.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2092,6 +2094,26 @@
       <c r="AI12" t="inlineStr">
         <is>
           <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Gammal grov död rönn trolig boplats / viloplats</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia # Gammal grov död rönn trolig boplats / viloplats</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2109,32 +2131,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126043322</v>
+        <v>126030775</v>
       </c>
       <c r="B13" t="n">
-        <v>56526</v>
+        <v>57933</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205992</v>
+        <v>103012</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2142,7 +2164,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>adult</t>
@@ -2150,20 +2171,24 @@
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fladdermusstation, Dlr</t>
+          <t>Lövskogsdel, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483330</v>
+        <v>483431</v>
       </c>
       <c r="R13" t="n">
-        <v>6664403</v>
+        <v>6664289</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2187,27 +2212,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>03:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>23:01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>8 st ljudupptagningar av Vattenfladdermus (Myotis daubentonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering av ljudfiler utförd av Emily Macgregor vid Naturcentrum.</t>
+          <t>03:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2221,32 +2241,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blandskog i branter</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Gammal grov död rönn trolig boplats / viloplats</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia # Gammal grov död rönn trolig boplats / viloplats</t>
+          <t>Barrblandskog med stort lövinslag i brant terräng som gränsar mot sumpskog / myrmark</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2261,6 +2261,757 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126062741</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56834</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Alsumpskog, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>483403</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6664267</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Uppflygande / ivägflaxande Järpe.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126068300</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57811</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Talldominerad del, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>483327</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6664235</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>59 st ljudupptagningar av mindre hackspett. Adult hane och hona observerad i skogen.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126062734</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57572</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lövskog Brant, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>483377</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6664402</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126062739</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56524</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>205988</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tajgafladdermus</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Myotis brandtii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Eversmann, 1845)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mitt i skogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>483451</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6664377</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126062735</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57501</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102975</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Hornuggla</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Asio otus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lövskog Brant, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>483377</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6664402</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126062738</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56519</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mitt i skogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>483451</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6664377</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>02:48</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>02:48</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Gles äldre lågvuxen granskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -1187,7 +1187,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126028950</v>
+        <v>126025893</v>
       </c>
       <c r="B6" t="n">
         <v>57811</v>
@@ -1217,27 +1217,31 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rifallet uppe i skogen, Dlr</t>
+          <t>Rifallet mot myr, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483381</v>
+        <v>483598</v>
       </c>
       <c r="R6" t="n">
-        <v>6664345</v>
+        <v>6664322</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1264,27 +1268,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>5 st ljudupptagningar av Talltita (poecile montanus).</t>
+          <t>12 st ljudupptagningar av Talltita (Poecile montanus) kl. 07.41 - kl. 09.15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1298,27 +1302,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Silverfura</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Sandtallskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1336,7 +1320,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126025893</v>
+        <v>126028950</v>
       </c>
       <c r="B7" t="n">
         <v>57811</v>
@@ -1366,31 +1350,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rifallet mot myr, Dlr</t>
+          <t>Rifallet uppe i skogen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483598</v>
+        <v>483381</v>
       </c>
       <c r="R7" t="n">
-        <v>6664322</v>
+        <v>6664345</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1417,27 +1397,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>12 st ljudupptagningar av Talltita (Poecile montanus) kl. 07.41 - kl. 09.15</t>
+          <t>5 st ljudupptagningar av Talltita (poecile montanus).</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1451,7 +1431,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Sandtallskog</t>
+          <t>Blandskog i branter</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Silverfura</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126043240</v>
+        <v>126030775</v>
       </c>
       <c r="B11" t="n">
-        <v>56519</v>
+        <v>57933</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,29 +1852,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205998</v>
+        <v>103012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1882,20 +1881,24 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fladdermusstation, Dlr</t>
+          <t>Lövskogsdel, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483330</v>
+        <v>483431</v>
       </c>
       <c r="R11" t="n">
-        <v>6664403</v>
+        <v>6664289</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1919,27 +1922,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>03:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>23:22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>12 st ljudupptagningar av Nordfladdermus (Eptesicus nilssonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering utförd av Emily Macgregor vid Naturcentrum.</t>
+          <t>03:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1953,12 +1951,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blandskog i branter</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
+          <t>Barrblandskog med stort lövinslag i brant terräng som gränsar mot sumpskog / myrmark</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1976,37 +1974,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126043322</v>
+        <v>126043240</v>
       </c>
       <c r="B12" t="n">
-        <v>56526</v>
+        <v>56519</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -2059,7 +2057,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2069,12 +2067,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>8 st ljudupptagningar av Vattenfladdermus (Myotis daubentonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering av ljudfiler utförd av Emily Macgregor vid Naturcentrum.</t>
+          <t>12 st ljudupptagningar av Nordfladdermus (Eptesicus nilssonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering utförd av Emily Macgregor vid Naturcentrum.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2094,26 +2092,6 @@
       <c r="AI12" t="inlineStr">
         <is>
           <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Gammal grov död rönn trolig boplats / viloplats</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia # Gammal grov död rönn trolig boplats / viloplats</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2131,32 +2109,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126030775</v>
+        <v>126043322</v>
       </c>
       <c r="B13" t="n">
-        <v>57933</v>
+        <v>56526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103012</v>
+        <v>205992</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2164,6 +2142,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>adult</t>
@@ -2171,24 +2150,20 @@
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lövskogsdel, Dlr</t>
+          <t>Fladdermusstation, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483431</v>
+        <v>483330</v>
       </c>
       <c r="R13" t="n">
-        <v>6664289</v>
+        <v>6664403</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2212,22 +2187,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>03:14</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>03:14</t>
+          <t>23:01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>8 st ljudupptagningar av Vattenfladdermus (Myotis daubentonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering av ljudfiler utförd av Emily Macgregor vid Naturcentrum.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2241,12 +2221,32 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrblandskog med stort lövinslag i brant terräng som gränsar mot sumpskog / myrmark</t>
+          <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Gammal grov död rönn trolig boplats / viloplats</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia # Gammal grov död rönn trolig boplats / viloplats</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -1841,10 +1841,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126030775</v>
+        <v>126043240</v>
       </c>
       <c r="B11" t="n">
-        <v>57933</v>
+        <v>56519</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,28 +1852,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103012</v>
+        <v>205998</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1881,24 +1882,20 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lövskogsdel, Dlr</t>
+          <t>Fladdermusstation, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483431</v>
+        <v>483330</v>
       </c>
       <c r="R11" t="n">
-        <v>6664289</v>
+        <v>6664403</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1922,22 +1919,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>03:14</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>03:14</t>
+          <t>23:22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>12 st ljudupptagningar av Nordfladdermus (Eptesicus nilssonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering utförd av Emily Macgregor vid Naturcentrum.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1951,12 +1953,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrblandskog med stort lövinslag i brant terräng som gränsar mot sumpskog / myrmark</t>
+          <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1974,37 +1976,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126043240</v>
+        <v>126043322</v>
       </c>
       <c r="B12" t="n">
-        <v>56519</v>
+        <v>56526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -2057,7 +2059,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2067,12 +2069,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>12 st ljudupptagningar av Nordfladdermus (Eptesicus nilssonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering utförd av Emily Macgregor vid Naturcentrum.</t>
+          <t>8 st ljudupptagningar av Vattenfladdermus (Myotis daubentonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering av ljudfiler utförd av Emily Macgregor vid Naturcentrum.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2092,6 +2094,26 @@
       <c r="AI12" t="inlineStr">
         <is>
           <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Gammal grov död rönn trolig boplats / viloplats</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia # Gammal grov död rönn trolig boplats / viloplats</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2109,32 +2131,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126043322</v>
+        <v>126030775</v>
       </c>
       <c r="B13" t="n">
-        <v>56526</v>
+        <v>57933</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205992</v>
+        <v>103012</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2142,7 +2164,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>adult</t>
@@ -2150,20 +2171,24 @@
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fladdermusstation, Dlr</t>
+          <t>Lövskogsdel, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483330</v>
+        <v>483431</v>
       </c>
       <c r="R13" t="n">
-        <v>6664403</v>
+        <v>6664289</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2187,27 +2212,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>03:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>23:01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>8 st ljudupptagningar av Vattenfladdermus (Myotis daubentonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering av ljudfiler utförd av Emily Macgregor vid Naturcentrum.</t>
+          <t>03:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2221,32 +2241,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blandskog i branter</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Gammal grov död rönn trolig boplats / viloplats</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia # Gammal grov död rönn trolig boplats / viloplats</t>
+          <t>Barrblandskog med stort lövinslag i brant terräng som gränsar mot sumpskog / myrmark</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126062741</v>
+        <v>126068300</v>
       </c>
       <c r="B14" t="n">
-        <v>56834</v>
+        <v>57811</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2275,42 +2275,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Alsumpskog, Dlr</t>
+          <t>Talldominerad del, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483403</v>
+        <v>483327</v>
       </c>
       <c r="R14" t="n">
-        <v>6664267</v>
+        <v>6664235</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2337,27 +2341,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Uppflygande / ivägflaxande Järpe.</t>
+          <t>59 st ljudupptagningar av mindre hackspett. Adult hane och hona observerad i skogen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2368,6 +2372,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2384,10 +2393,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126068300</v>
+        <v>126062741</v>
       </c>
       <c r="B15" t="n">
-        <v>57811</v>
+        <v>56834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2395,46 +2404,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Talldominerad del, Dlr</t>
+          <t>Alsumpskog, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483327</v>
+        <v>483403</v>
       </c>
       <c r="R15" t="n">
-        <v>6664235</v>
+        <v>6664267</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2461,27 +2466,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>59 st ljudupptagningar av mindre hackspett. Adult hane och hona observerad i skogen.</t>
+          <t>Uppflygande / ivägflaxande Järpe.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2492,11 +2497,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -1841,10 +1841,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126043240</v>
+        <v>126030775</v>
       </c>
       <c r="B11" t="n">
-        <v>56519</v>
+        <v>57933</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,29 +1852,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205998</v>
+        <v>103012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1882,20 +1881,24 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fladdermusstation, Dlr</t>
+          <t>Lövskogsdel, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483330</v>
+        <v>483431</v>
       </c>
       <c r="R11" t="n">
-        <v>6664403</v>
+        <v>6664289</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1919,27 +1922,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>03:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>23:22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>12 st ljudupptagningar av Nordfladdermus (Eptesicus nilssonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering utförd av Emily Macgregor vid Naturcentrum.</t>
+          <t>03:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1953,12 +1951,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blandskog i branter</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
+          <t>Barrblandskog med stort lövinslag i brant terräng som gränsar mot sumpskog / myrmark</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1976,37 +1974,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126043322</v>
+        <v>126043240</v>
       </c>
       <c r="B12" t="n">
-        <v>56526</v>
+        <v>56519</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -2059,7 +2057,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2069,12 +2067,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>8 st ljudupptagningar av Vattenfladdermus (Myotis daubentonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering av ljudfiler utförd av Emily Macgregor vid Naturcentrum.</t>
+          <t>12 st ljudupptagningar av Nordfladdermus (Eptesicus nilssonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering utförd av Emily Macgregor vid Naturcentrum.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2094,26 +2092,6 @@
       <c r="AI12" t="inlineStr">
         <is>
           <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Gammal grov död rönn trolig boplats / viloplats</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia # Gammal grov död rönn trolig boplats / viloplats</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2131,32 +2109,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126030775</v>
+        <v>126043322</v>
       </c>
       <c r="B13" t="n">
-        <v>57933</v>
+        <v>56526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103012</v>
+        <v>205992</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2164,6 +2142,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>adult</t>
@@ -2171,24 +2150,20 @@
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lövskogsdel, Dlr</t>
+          <t>Fladdermusstation, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483431</v>
+        <v>483330</v>
       </c>
       <c r="R13" t="n">
-        <v>6664289</v>
+        <v>6664403</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2212,22 +2187,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>03:14</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>03:14</t>
+          <t>23:01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>8 st ljudupptagningar av Vattenfladdermus (Myotis daubentonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering av ljudfiler utförd av Emily Macgregor vid Naturcentrum.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2241,12 +2221,32 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrblandskog med stort lövinslag i brant terräng som gränsar mot sumpskog / myrmark</t>
+          <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Gammal grov död rönn trolig boplats / viloplats</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia # Gammal grov död rönn trolig boplats / viloplats</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126068300</v>
+        <v>126062741</v>
       </c>
       <c r="B14" t="n">
-        <v>57811</v>
+        <v>56834</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2275,46 +2275,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Talldominerad del, Dlr</t>
+          <t>Alsumpskog, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483327</v>
+        <v>483403</v>
       </c>
       <c r="R14" t="n">
-        <v>6664235</v>
+        <v>6664267</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2341,27 +2337,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>59 st ljudupptagningar av mindre hackspett. Adult hane och hona observerad i skogen.</t>
+          <t>Uppflygande / ivägflaxande Järpe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2372,11 +2368,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2393,10 +2384,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126062741</v>
+        <v>126068300</v>
       </c>
       <c r="B15" t="n">
-        <v>56834</v>
+        <v>57811</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2404,42 +2395,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Alsumpskog, Dlr</t>
+          <t>Talldominerad del, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483403</v>
+        <v>483327</v>
       </c>
       <c r="R15" t="n">
-        <v>6664267</v>
+        <v>6664235</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2466,27 +2461,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Uppflygande / ivägflaxande Järpe.</t>
+          <t>59 st ljudupptagningar av mindre hackspett. Adult hane och hona observerad i skogen.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2497,6 +2492,11 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>126028545</v>
       </c>
       <c r="B3" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>126026452</v>
       </c>
       <c r="B4" t="n">
-        <v>57809</v>
+        <v>57810</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126027986</v>
       </c>
       <c r="B5" t="n">
-        <v>56834</v>
+        <v>56835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>126025893</v>
       </c>
       <c r="B6" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>126028950</v>
       </c>
       <c r="B7" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>126026768</v>
       </c>
       <c r="B8" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>126027361</v>
       </c>
       <c r="B9" t="n">
-        <v>57664</v>
+        <v>57665</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>126029030</v>
       </c>
       <c r="B10" t="n">
-        <v>57473</v>
+        <v>57474</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>126030775</v>
       </c>
       <c r="B11" t="n">
-        <v>57933</v>
+        <v>57934</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>126043240</v>
       </c>
       <c r="B12" t="n">
-        <v>56519</v>
+        <v>56520</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>126043322</v>
       </c>
       <c r="B13" t="n">
-        <v>56526</v>
+        <v>56527</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2264,10 +2264,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126062741</v>
+        <v>126068300</v>
       </c>
       <c r="B14" t="n">
-        <v>56834</v>
+        <v>57812</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2275,42 +2275,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Alsumpskog, Dlr</t>
+          <t>Talldominerad del, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483403</v>
+        <v>483327</v>
       </c>
       <c r="R14" t="n">
-        <v>6664267</v>
+        <v>6664235</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2337,27 +2341,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Uppflygande / ivägflaxande Järpe.</t>
+          <t>59 st ljudupptagningar av mindre hackspett. Adult hane och hona observerad i skogen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2368,6 +2372,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2384,10 +2393,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126068300</v>
+        <v>126062741</v>
       </c>
       <c r="B15" t="n">
-        <v>57811</v>
+        <v>56835</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2395,46 +2404,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Talldominerad del, Dlr</t>
+          <t>Alsumpskog, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483327</v>
+        <v>483403</v>
       </c>
       <c r="R15" t="n">
-        <v>6664235</v>
+        <v>6664267</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2461,27 +2466,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>59 st ljudupptagningar av mindre hackspett. Adult hane och hona observerad i skogen.</t>
+          <t>Uppflygande / ivägflaxande Järpe.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2492,11 +2497,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2516,7 +2516,7 @@
         <v>126062734</v>
       </c>
       <c r="B16" t="n">
-        <v>57572</v>
+        <v>57573</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>126062739</v>
       </c>
       <c r="B17" t="n">
-        <v>56524</v>
+        <v>56525</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>126062735</v>
       </c>
       <c r="B18" t="n">
-        <v>57501</v>
+        <v>57502</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>126062738</v>
       </c>
       <c r="B19" t="n">
-        <v>56519</v>
+        <v>56520</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -1841,10 +1841,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126030775</v>
+        <v>126043240</v>
       </c>
       <c r="B11" t="n">
-        <v>57934</v>
+        <v>56520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,28 +1852,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103012</v>
+        <v>205998</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1881,24 +1882,20 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lövskogsdel, Dlr</t>
+          <t>Fladdermusstation, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483431</v>
+        <v>483330</v>
       </c>
       <c r="R11" t="n">
-        <v>6664289</v>
+        <v>6664403</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1922,22 +1919,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>03:14</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>03:14</t>
+          <t>23:22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>12 st ljudupptagningar av Nordfladdermus (Eptesicus nilssonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering utförd av Emily Macgregor vid Naturcentrum.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1951,12 +1953,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrblandskog med stort lövinslag i brant terräng som gränsar mot sumpskog / myrmark</t>
+          <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1974,37 +1976,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126043240</v>
+        <v>126043322</v>
       </c>
       <c r="B12" t="n">
-        <v>56520</v>
+        <v>56527</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -2057,7 +2059,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2067,12 +2069,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>12 st ljudupptagningar av Nordfladdermus (Eptesicus nilssonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering utförd av Emily Macgregor vid Naturcentrum.</t>
+          <t>8 st ljudupptagningar av Vattenfladdermus (Myotis daubentonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering av ljudfiler utförd av Emily Macgregor vid Naturcentrum.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2092,6 +2094,26 @@
       <c r="AI12" t="inlineStr">
         <is>
           <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Gammal grov död rönn trolig boplats / viloplats</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia # Gammal grov död rönn trolig boplats / viloplats</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2109,32 +2131,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126043322</v>
+        <v>126030775</v>
       </c>
       <c r="B13" t="n">
-        <v>56527</v>
+        <v>57934</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205992</v>
+        <v>103012</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2142,7 +2164,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>adult</t>
@@ -2150,20 +2171,24 @@
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fladdermusstation, Dlr</t>
+          <t>Lövskogsdel, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483330</v>
+        <v>483431</v>
       </c>
       <c r="R13" t="n">
-        <v>6664403</v>
+        <v>6664289</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2187,27 +2212,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>03:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>23:01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>8 st ljudupptagningar av Vattenfladdermus (Myotis daubentonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering av ljudfiler utförd av Emily Macgregor vid Naturcentrum.</t>
+          <t>03:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2221,32 +2241,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blandskog i branter</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Gammal grov död rönn trolig boplats / viloplats</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia # Gammal grov död rönn trolig boplats / viloplats</t>
+          <t>Barrblandskog med stort lövinslag i brant terräng som gränsar mot sumpskog / myrmark</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -1841,10 +1841,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126043240</v>
+        <v>126030775</v>
       </c>
       <c r="B11" t="n">
-        <v>56520</v>
+        <v>57934</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,29 +1852,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205998</v>
+        <v>103012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1882,20 +1881,24 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fladdermusstation, Dlr</t>
+          <t>Lövskogsdel, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483330</v>
+        <v>483431</v>
       </c>
       <c r="R11" t="n">
-        <v>6664403</v>
+        <v>6664289</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1919,27 +1922,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>03:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>23:22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>12 st ljudupptagningar av Nordfladdermus (Eptesicus nilssonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering utförd av Emily Macgregor vid Naturcentrum.</t>
+          <t>03:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1953,12 +1951,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blandskog i branter</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
+          <t>Barrblandskog med stort lövinslag i brant terräng som gränsar mot sumpskog / myrmark</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1976,37 +1974,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126043322</v>
+        <v>126043240</v>
       </c>
       <c r="B12" t="n">
-        <v>56527</v>
+        <v>56520</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -2059,7 +2057,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2069,12 +2067,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>8 st ljudupptagningar av Vattenfladdermus (Myotis daubentonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering av ljudfiler utförd av Emily Macgregor vid Naturcentrum.</t>
+          <t>12 st ljudupptagningar av Nordfladdermus (Eptesicus nilssonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering utförd av Emily Macgregor vid Naturcentrum.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2094,26 +2092,6 @@
       <c r="AI12" t="inlineStr">
         <is>
           <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Gammal grov död rönn trolig boplats / viloplats</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia # Gammal grov död rönn trolig boplats / viloplats</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2131,32 +2109,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126030775</v>
+        <v>126043322</v>
       </c>
       <c r="B13" t="n">
-        <v>57934</v>
+        <v>56527</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103012</v>
+        <v>205992</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2164,6 +2142,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>adult</t>
@@ -2171,24 +2150,20 @@
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lövskogsdel, Dlr</t>
+          <t>Fladdermusstation, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483431</v>
+        <v>483330</v>
       </c>
       <c r="R13" t="n">
-        <v>6664289</v>
+        <v>6664403</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2212,22 +2187,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>03:14</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>03:14</t>
+          <t>23:01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>8 st ljudupptagningar av Vattenfladdermus (Myotis daubentonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering av ljudfiler utförd av Emily Macgregor vid Naturcentrum.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2241,12 +2221,32 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrblandskog med stort lövinslag i brant terräng som gränsar mot sumpskog / myrmark</t>
+          <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Gammal grov död rönn trolig boplats / viloplats</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia # Gammal grov död rönn trolig boplats / viloplats</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126068300</v>
+        <v>126062741</v>
       </c>
       <c r="B14" t="n">
-        <v>57812</v>
+        <v>56835</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2275,46 +2275,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Talldominerad del, Dlr</t>
+          <t>Alsumpskog, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483327</v>
+        <v>483403</v>
       </c>
       <c r="R14" t="n">
-        <v>6664235</v>
+        <v>6664267</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2341,27 +2337,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>59 st ljudupptagningar av mindre hackspett. Adult hane och hona observerad i skogen.</t>
+          <t>Uppflygande / ivägflaxande Järpe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2372,11 +2368,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2393,10 +2384,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126062741</v>
+        <v>126068300</v>
       </c>
       <c r="B15" t="n">
-        <v>56835</v>
+        <v>57812</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2404,42 +2395,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Alsumpskog, Dlr</t>
+          <t>Talldominerad del, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483403</v>
+        <v>483327</v>
       </c>
       <c r="R15" t="n">
-        <v>6664267</v>
+        <v>6664235</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2466,27 +2461,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Uppflygande / ivägflaxande Järpe.</t>
+          <t>59 st ljudupptagningar av mindre hackspett. Adult hane och hona observerad i skogen.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2497,6 +2492,11 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>126028545</v>
       </c>
       <c r="B3" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>126026452</v>
       </c>
       <c r="B4" t="n">
-        <v>57810</v>
+        <v>57814</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126027986</v>
       </c>
       <c r="B5" t="n">
-        <v>56835</v>
+        <v>56839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>126025893</v>
       </c>
       <c r="B6" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>126028950</v>
       </c>
       <c r="B7" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>126026768</v>
       </c>
       <c r="B8" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>126027361</v>
       </c>
       <c r="B9" t="n">
-        <v>57665</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>126029030</v>
       </c>
       <c r="B10" t="n">
-        <v>57474</v>
+        <v>57478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126043240</v>
+        <v>126030775</v>
       </c>
       <c r="B11" t="n">
-        <v>56520</v>
+        <v>57938</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,29 +1852,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205998</v>
+        <v>103012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1882,20 +1881,24 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fladdermusstation, Dlr</t>
+          <t>Lövskogsdel, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483330</v>
+        <v>483431</v>
       </c>
       <c r="R11" t="n">
-        <v>6664403</v>
+        <v>6664289</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1919,27 +1922,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>03:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>23:22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>12 st ljudupptagningar av Nordfladdermus (Eptesicus nilssonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering utförd av Emily Macgregor vid Naturcentrum.</t>
+          <t>03:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1953,12 +1951,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blandskog i branter</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
+          <t>Barrblandskog med stort lövinslag i brant terräng som gränsar mot sumpskog / myrmark</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1976,37 +1974,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126043322</v>
+        <v>126043240</v>
       </c>
       <c r="B12" t="n">
-        <v>56527</v>
+        <v>56524</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -2059,7 +2057,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2069,12 +2067,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>8 st ljudupptagningar av Vattenfladdermus (Myotis daubentonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering av ljudfiler utförd av Emily Macgregor vid Naturcentrum.</t>
+          <t>12 st ljudupptagningar av Nordfladdermus (Eptesicus nilssonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering utförd av Emily Macgregor vid Naturcentrum.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2094,26 +2092,6 @@
       <c r="AI12" t="inlineStr">
         <is>
           <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Gammal grov död rönn trolig boplats / viloplats</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia # Gammal grov död rönn trolig boplats / viloplats</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2131,32 +2109,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126030775</v>
+        <v>126043322</v>
       </c>
       <c r="B13" t="n">
-        <v>57934</v>
+        <v>56531</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103012</v>
+        <v>205992</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2164,6 +2142,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>adult</t>
@@ -2171,24 +2150,20 @@
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lövskogsdel, Dlr</t>
+          <t>Fladdermusstation, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483431</v>
+        <v>483330</v>
       </c>
       <c r="R13" t="n">
-        <v>6664289</v>
+        <v>6664403</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2212,22 +2187,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>03:14</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>03:14</t>
+          <t>23:01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>8 st ljudupptagningar av Vattenfladdermus (Myotis daubentonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering av ljudfiler utförd av Emily Macgregor vid Naturcentrum.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2241,12 +2221,32 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrblandskog med stort lövinslag i brant terräng som gränsar mot sumpskog / myrmark</t>
+          <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Gammal grov död rönn trolig boplats / viloplats</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia # Gammal grov död rönn trolig boplats / viloplats</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126062741</v>
+        <v>126068300</v>
       </c>
       <c r="B14" t="n">
-        <v>56835</v>
+        <v>57816</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2275,42 +2275,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Alsumpskog, Dlr</t>
+          <t>Talldominerad del, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483403</v>
+        <v>483327</v>
       </c>
       <c r="R14" t="n">
-        <v>6664267</v>
+        <v>6664235</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2337,27 +2341,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Uppflygande / ivägflaxande Järpe.</t>
+          <t>59 st ljudupptagningar av mindre hackspett. Adult hane och hona observerad i skogen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2368,6 +2372,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2384,10 +2393,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126068300</v>
+        <v>126062741</v>
       </c>
       <c r="B15" t="n">
-        <v>57812</v>
+        <v>56839</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2395,46 +2404,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Talldominerad del, Dlr</t>
+          <t>Alsumpskog, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483327</v>
+        <v>483403</v>
       </c>
       <c r="R15" t="n">
-        <v>6664235</v>
+        <v>6664267</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2461,27 +2466,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>59 st ljudupptagningar av mindre hackspett. Adult hane och hona observerad i skogen.</t>
+          <t>Uppflygande / ivägflaxande Järpe.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2492,11 +2497,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2516,7 +2516,7 @@
         <v>126062734</v>
       </c>
       <c r="B16" t="n">
-        <v>57573</v>
+        <v>57577</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>126062739</v>
       </c>
       <c r="B17" t="n">
-        <v>56525</v>
+        <v>56529</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>126062735</v>
       </c>
       <c r="B18" t="n">
-        <v>57502</v>
+        <v>57506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>126062738</v>
       </c>
       <c r="B19" t="n">
-        <v>56520</v>
+        <v>56524</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -2264,10 +2264,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126068300</v>
+        <v>126062741</v>
       </c>
       <c r="B14" t="n">
-        <v>57816</v>
+        <v>56839</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2275,46 +2275,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Talldominerad del, Dlr</t>
+          <t>Alsumpskog, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483327</v>
+        <v>483403</v>
       </c>
       <c r="R14" t="n">
-        <v>6664235</v>
+        <v>6664267</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2341,27 +2337,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>59 st ljudupptagningar av mindre hackspett. Adult hane och hona observerad i skogen.</t>
+          <t>Uppflygande / ivägflaxande Järpe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2372,11 +2368,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2393,10 +2384,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126062741</v>
+        <v>126068300</v>
       </c>
       <c r="B15" t="n">
-        <v>56839</v>
+        <v>57816</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2404,42 +2395,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Alsumpskog, Dlr</t>
+          <t>Talldominerad del, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483403</v>
+        <v>483327</v>
       </c>
       <c r="R15" t="n">
-        <v>6664267</v>
+        <v>6664235</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2466,27 +2461,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Uppflygande / ivägflaxande Järpe.</t>
+          <t>59 st ljudupptagningar av mindre hackspett. Adult hane och hona observerad i skogen.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2497,6 +2492,11 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -2264,10 +2264,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126062741</v>
+        <v>126068300</v>
       </c>
       <c r="B14" t="n">
-        <v>56839</v>
+        <v>57816</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2275,42 +2275,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Alsumpskog, Dlr</t>
+          <t>Talldominerad del, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483403</v>
+        <v>483327</v>
       </c>
       <c r="R14" t="n">
-        <v>6664267</v>
+        <v>6664235</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2337,27 +2341,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Uppflygande / ivägflaxande Järpe.</t>
+          <t>59 st ljudupptagningar av mindre hackspett. Adult hane och hona observerad i skogen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2368,6 +2372,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2384,10 +2393,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126068300</v>
+        <v>126062741</v>
       </c>
       <c r="B15" t="n">
-        <v>57816</v>
+        <v>56839</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2395,46 +2404,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Talldominerad del, Dlr</t>
+          <t>Alsumpskog, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483327</v>
+        <v>483403</v>
       </c>
       <c r="R15" t="n">
-        <v>6664235</v>
+        <v>6664267</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2461,27 +2466,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>59 st ljudupptagningar av mindre hackspett. Adult hane och hona observerad i skogen.</t>
+          <t>Uppflygande / ivägflaxande Järpe.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2492,11 +2497,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>126028545</v>
       </c>
       <c r="B3" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>126026452</v>
       </c>
       <c r="B4" t="n">
-        <v>57814</v>
+        <v>57815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126027986</v>
       </c>
       <c r="B5" t="n">
-        <v>56839</v>
+        <v>56840</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>126025893</v>
       </c>
       <c r="B6" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>126028950</v>
       </c>
       <c r="B7" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>126026768</v>
       </c>
       <c r="B8" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>126027361</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>126029030</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57479</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>126030775</v>
       </c>
       <c r="B11" t="n">
-        <v>57938</v>
+        <v>57939</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>126043240</v>
       </c>
       <c r="B12" t="n">
-        <v>56524</v>
+        <v>56525</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>126043322</v>
       </c>
       <c r="B13" t="n">
-        <v>56531</v>
+        <v>56532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>126062741</v>
       </c>
       <c r="B14" t="n">
-        <v>56839</v>
+        <v>56840</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>126068300</v>
       </c>
       <c r="B15" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>126062734</v>
       </c>
       <c r="B16" t="n">
-        <v>57577</v>
+        <v>57578</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>126062739</v>
       </c>
       <c r="B17" t="n">
-        <v>56529</v>
+        <v>56530</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>126062735</v>
       </c>
       <c r="B18" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>126062738</v>
       </c>
       <c r="B19" t="n">
-        <v>56524</v>
+        <v>56525</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>126026452</v>
       </c>
       <c r="B4" t="n">
-        <v>57815</v>
+        <v>57830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,11 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1036,7 +1040,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2 st ljudupptagningar av Talltita (Poecile montanus).</t>
+          <t>Åtskilliga ljudupptagningar av entita under flera dygn.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2387,7 +2391,7 @@
         <v>126068300</v>
       </c>
       <c r="B15" t="n">
-        <v>57817</v>
+        <v>57832</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2423,7 +2427,11 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2481,7 +2489,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>59 st ljudupptagningar av mindre hackspett. Adult hane och hona observerad i skogen.</t>
+          <t>Åtskilliga ljudupptagningar av talltita under flera dygn.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>126026452</v>
       </c>
       <c r="B4" t="n">
-        <v>57830</v>
+        <v>57831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>126068300</v>
       </c>
       <c r="B15" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>126026452</v>
       </c>
       <c r="B4" t="n">
-        <v>57831</v>
+        <v>57843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>126068300</v>
       </c>
       <c r="B15" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>126026452</v>
       </c>
       <c r="B4" t="n">
-        <v>57843</v>
+        <v>57847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>126068300</v>
       </c>
       <c r="B15" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>126026452</v>
       </c>
       <c r="B4" t="n">
-        <v>57847</v>
+        <v>57874</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>126068300</v>
       </c>
       <c r="B15" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>126026452</v>
       </c>
       <c r="B4" t="n">
-        <v>57874</v>
+        <v>57878</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>126068300</v>
       </c>
       <c r="B15" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -2648,7 +2648,7 @@
         <v>126062739</v>
       </c>
       <c r="B17" t="n">
-        <v>56530</v>
+        <v>56603</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2656,23 +2656,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205988</v>
+        <v>232474</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tajgafladdermus</t>
+          <t>Mustaschfladdermus/tajgafladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Myotis brandtii</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Eversmann, 1845)</t>
-        </is>
-      </c>
+          <t>Myotis mystacinus/brandtii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>1</t>

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -2648,7 +2648,7 @@
         <v>126062739</v>
       </c>
       <c r="B17" t="n">
-        <v>56603</v>
+        <v>56606</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -2648,7 +2648,7 @@
         <v>126062739</v>
       </c>
       <c r="B17" t="n">
-        <v>56606</v>
+        <v>56611</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -2648,7 +2648,7 @@
         <v>126062739</v>
       </c>
       <c r="B17" t="n">
-        <v>56611</v>
+        <v>56612</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -2648,7 +2648,7 @@
         <v>126062739</v>
       </c>
       <c r="B17" t="n">
-        <v>56612</v>
+        <v>56615</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 23658-2025 artfynd.xlsx
+++ b/artfynd/A 23658-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>96668543</v>
       </c>
       <c r="B2" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483436.0615340461</v>
+        <v>483436</v>
       </c>
       <c r="R2" t="n">
-        <v>6664173.689955195</v>
+        <v>6664174</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,19 +746,9 @@
           <t>2021-10-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -811,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126028545</v>
+        <v>126026768</v>
       </c>
       <c r="B3" t="n">
-        <v>56849</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -851,17 +836,21 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rifallet uppe i skogen, Dlr</t>
+          <t>Rifallet upp från mossen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483381</v>
+        <v>483559</v>
       </c>
       <c r="R3" t="n">
-        <v>6664345</v>
+        <v>6664311</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -888,27 +877,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>03:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>03:01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>3 st ljudupptagningar av tjäderläten / sångljud.</t>
+          <t>Tre ljudupptagningar av tjäder mellan kl. 03.01 - kl. 04.54 den 15 juni 2025.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,37 +924,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126026452</v>
+        <v>126028425</v>
       </c>
       <c r="B4" t="n">
-        <v>57878</v>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -974,26 +963,18 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rifallet upp från mossen, Dlr</t>
+          <t>Rifallet uppe i skogen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483559</v>
+        <v>483381</v>
       </c>
       <c r="R4" t="n">
-        <v>6664311</v>
+        <v>6664345</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1025,22 +1006,22 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>02:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>02:59</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Åtskilliga ljudupptagningar av entita under flera dygn.</t>
+          <t>3 st ljudupptagningar av tjäderläten / sångljud.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,6 +1032,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1067,27 +1053,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126027986</v>
+        <v>126029030</v>
       </c>
       <c r="B5" t="n">
-        <v>56840</v>
+        <v>57774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>102976</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1110,14 +1096,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rifallet upp från mossen, Dlr</t>
+          <t>Rifallet uppe i skogen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483559</v>
+        <v>483381</v>
       </c>
       <c r="R5" t="n">
-        <v>6664311</v>
+        <v>6664345</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1149,7 +1135,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>03:14</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1159,12 +1145,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>03:14</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>3 st ljudupptagningar av Järpe (Tetrastes bonasia). En av ljudfilerna uppladdade på Xeno-canto.</t>
+          <t>Ljudupptagning av tornseglare på nära håll i gles sluttande barrskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1191,61 +1177,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126025893</v>
+        <v>126066837</v>
       </c>
       <c r="B6" t="n">
-        <v>57817</v>
+        <v>57774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>102976</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rifallet mot myr, Dlr</t>
+          <t>Sumpskog nedan ekonomibyggnader, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483598</v>
+        <v>483266</v>
       </c>
       <c r="R6" t="n">
-        <v>6664322</v>
+        <v>6664386</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1272,27 +1250,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>12 st ljudupptagningar av Talltita (Poecile montanus) kl. 07.41 - kl. 09.15</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1303,11 +1276,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1324,10 +1292,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126028950</v>
+        <v>126030775</v>
       </c>
       <c r="B7" t="n">
-        <v>57817</v>
+        <v>58238</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,49 +1303,53 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rifallet uppe i skogen, Dlr</t>
+          <t>Lövskogsdel, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483381</v>
+        <v>483431</v>
       </c>
       <c r="R7" t="n">
-        <v>6664345</v>
+        <v>6664289</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1406,7 +1378,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>03:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1416,12 +1388,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>5 st ljudupptagningar av Talltita (poecile montanus).</t>
+          <t>03:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1440,22 +1407,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Silverfura</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Barrblandskog med stort lövinslag i brant terräng som gränsar mot sumpskog / myrmark</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1473,37 +1425,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126026768</v>
+        <v>126026452</v>
       </c>
       <c r="B8" t="n">
-        <v>56849</v>
+        <v>58112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1512,7 +1464,11 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1554,27 +1510,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>03:01</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>03:01</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Tre ljudupptagningar av tjäder mellan kl. 03.01 - kl. 04.54 den 15 juni 2025.</t>
+          <t>Åtskilliga ljudupptagningar av entita under flera dygn.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1601,10 +1557,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126027361</v>
+        <v>126066185</v>
       </c>
       <c r="B9" t="n">
-        <v>57670</v>
+        <v>58112</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,16 +1568,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1640,14 +1596,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rifallet upp från mossen, Dlr</t>
+          <t>Sumpskog nedan ekonomibyggnader, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483559</v>
+        <v>483266</v>
       </c>
       <c r="R9" t="n">
-        <v>6664311</v>
+        <v>6664386</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1674,7 +1630,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1684,7 +1640,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1692,11 +1648,6 @@
           <t>07:01</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>49 st ljudupptagningar av mindre hackspett (Dryobates minor)</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1705,6 +1656,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1721,40 +1677,44 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126029030</v>
+        <v>126025893</v>
       </c>
       <c r="B10" t="n">
-        <v>57479</v>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102976</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
@@ -1764,14 +1724,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rifallet uppe i skogen, Dlr</t>
+          <t>Rifallet mot myr, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483381</v>
+        <v>483598</v>
       </c>
       <c r="R10" t="n">
-        <v>6664345</v>
+        <v>6664322</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1803,22 +1763,22 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ljudupptagning av tornseglare på nära håll i gles sluttande barrskog.</t>
+          <t>12 st ljudupptagningar av Talltita (Poecile montanus) kl. 07.41 - kl. 09.15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1829,6 +1789,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1845,10 +1810,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126030775</v>
+        <v>126028950</v>
       </c>
       <c r="B11" t="n">
-        <v>57939</v>
+        <v>58114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,53 +1821,49 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103012</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lövskogsdel, Dlr</t>
+          <t>Rifallet uppe i skogen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483431</v>
+        <v>483381</v>
       </c>
       <c r="R11" t="n">
-        <v>6664289</v>
+        <v>6664345</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1931,7 +1892,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>03:14</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1941,7 +1902,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>03:14</t>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>5 st ljudupptagningar av Talltita (poecile montanus).</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1960,7 +1926,22 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrblandskog med stort lövinslag i brant terräng som gränsar mot sumpskog / myrmark</t>
+          <t>Silverfura</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1978,10 +1959,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126043240</v>
+        <v>126066371</v>
       </c>
       <c r="B12" t="n">
-        <v>56525</v>
+        <v>58114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1989,47 +1970,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205998</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fladdermusstation, Dlr</t>
+          <t>Sumpskog nedan ekonomibyggnader, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483330</v>
+        <v>483266</v>
       </c>
       <c r="R12" t="n">
-        <v>6664403</v>
+        <v>6664386</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2056,27 +2032,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>23:22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>12 st ljudupptagningar av Nordfladdermus (Eptesicus nilssonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering utförd av Emily Macgregor vid Naturcentrum.</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2090,12 +2061,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2113,58 +2079,61 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126043322</v>
+        <v>126068300</v>
       </c>
       <c r="B13" t="n">
-        <v>56532</v>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205992</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fladdermusstation, Dlr</t>
+          <t>Talldominerad del, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483330</v>
+        <v>483327</v>
       </c>
       <c r="R13" t="n">
-        <v>6664403</v>
+        <v>6664235</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2191,27 +2160,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>8 st ljudupptagningar av Vattenfladdermus (Myotis daubentonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering av ljudfiler utförd av Emily Macgregor vid Naturcentrum.</t>
+          <t>Åtskilliga ljudupptagningar av talltita under flera dygn.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2225,32 +2194,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Gammal grov död rönn trolig boplats / viloplats</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia # Gammal grov död rönn trolig boplats / viloplats</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2268,32 +2212,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126062741</v>
+        <v>126043322</v>
       </c>
       <c r="B14" t="n">
-        <v>56840</v>
+        <v>56823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>205992</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2301,20 +2245,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Alsumpskog, Dlr</t>
+          <t>Fladdermusstation, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483403</v>
+        <v>483330</v>
       </c>
       <c r="R14" t="n">
-        <v>6664267</v>
+        <v>6664403</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2346,7 +2295,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2356,12 +2305,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Uppflygande / ivägflaxande Järpe.</t>
+          <t>8 st ljudupptagningar av Vattenfladdermus (Myotis daubentonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering av ljudfiler utförd av Emily Macgregor vid Naturcentrum.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2372,6 +2321,36 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Gammal grov död rönn trolig boplats / viloplats</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia # Gammal grov död rönn trolig boplats / viloplats</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2388,10 +2367,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126068300</v>
+        <v>126043240</v>
       </c>
       <c r="B15" t="n">
-        <v>57880</v>
+        <v>56816</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2399,21 +2378,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>205998</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2421,28 +2400,25 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Talldominerad del, Dlr</t>
+          <t>Fladdermusstation, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483327</v>
+        <v>483330</v>
       </c>
       <c r="R15" t="n">
-        <v>6664235</v>
+        <v>6664403</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2469,27 +2445,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Åtskilliga ljudupptagningar av talltita under flera dygn.</t>
+          <t>12 st ljudupptagningar av Nordfladdermus (Eptesicus nilssonii) med Autobox och Petterson u384 ultraljudsmikrofon. Artbestämning och verifiering utförd av Emily Macgregor vid Naturcentrum.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2503,7 +2479,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kuperad blandskog nära sumpmark med vattenspeglar och visst rörligt markvatten.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2521,10 +2502,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126062734</v>
+        <v>126062738</v>
       </c>
       <c r="B16" t="n">
-        <v>57578</v>
+        <v>56816</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2532,21 +2513,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100001</v>
+        <v>205998</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2554,6 +2535,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>adult</t>
@@ -2564,14 +2546,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lövskog Brant, Dlr</t>
+          <t>Mitt i skogen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483377</v>
+        <v>483451</v>
       </c>
       <c r="R16" t="n">
-        <v>6664402</v>
+        <v>6664377</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2603,7 +2585,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>02:35</t>
+          <t>02:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2613,7 +2595,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>02:35</t>
+          <t>02:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2627,7 +2609,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Gles äldre lågvuxen granskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2642,380 +2629,6 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>126062739</v>
-      </c>
-      <c r="B17" t="n">
-        <v>56615</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>232474</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Mustaschfladdermus/tajgafladdermus</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Myotis mystacinus/brandtii</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Mitt i skogen, Dlr</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>483451</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6664377</v>
-      </c>
-      <c r="S17" t="n">
-        <v>5</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Ludvika</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Grangärde</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>02:15</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>02:15</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Egil Borgne</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Egil Borgne</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>126062735</v>
-      </c>
-      <c r="B18" t="n">
-        <v>57507</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>102975</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Hornuggla</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Asio otus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Lövskog Brant, Dlr</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>483377</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6664402</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Ludvika</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Grangärde</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Egil Borgne</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Egil Borgne</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>126062738</v>
-      </c>
-      <c r="B19" t="n">
-        <v>56525</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Eptesicus nilssonii</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Mitt i skogen, Dlr</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>483451</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6664377</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Ludvika</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Grangärde</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>02:48</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>02:48</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Gles äldre lågvuxen granskog</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Egil Borgne</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Egil Borgne</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
